--- a/docs/reports/20261017_稽核結案對帳_明細.xlsx
+++ b/docs/reports/20261017_稽核結案對帳_明細.xlsx
@@ -44806,7 +44806,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>v14.1 報告留下：L1_MFleet_P25Lo／Hi 顯示用區間沒有比照截斷（D 欄 0.1066 低於同單價下限約 0.125）；Interface 第 321–327 列 18 格追蹤文字變動；Har_In 第 20、32 列只清旗標值；測試函式名稱沿用；Decisions 分六筆。</t>
+          <t>v14.1 報告留下：L1_MFleet_P25Lo／Hi 顯示用區間沒有比照截斷（D 欄 0.1066 低於同單價下限約 0.125）；Interface 第 321–327 列 18 格追蹤文字變動；Har_In 第 20、32 列只清旗標值；測試函式名稱沿用；Decisions 分六筆。master 上的 v14.1 獨立查核（20261017_v14.1_獨立查核.md）已確認與建置報告不符 0 項，故獨立查核本身已完成。</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
